--- a/Docs/ORD_Data_Spec.xlsx
+++ b/Docs/ORD_Data_Spec.xlsx
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="B1:H59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -10477,8 +10477,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
     <row r="13">
       <c r="B13" s="89" t="n"/>
     </row>
@@ -10984,7 +10982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J19"/>
+  <dimension ref="B1:I19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -11003,7 +11001,7 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>ORD v2 note: perspective_code is a free string, not a locked enum. Well-known Oasis/OED values are gul, il, ri. The list below is illustrative of possible perspectives, not exhaustive or fixed.</t>
+          <t>ORD v2 note: perspective_code is a free string, not a locked enum. Well-known Oasis/OED values are gul, il, ri (reinsurance net, i.e. cedant's retained loss), and rl (reinsurance loss, i.e. ceded amount recovered from reinsurers). The list below is illustrative of possible perspectives, not exhaustive or fixed.</t>
         </is>
       </c>
     </row>

--- a/Docs/ORD_Data_Spec.xlsx
+++ b/Docs/ORD_Data_Spec.xlsx
@@ -2477,7 +2477,7 @@
       <c r="BP12" s="66" t="n"/>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>EPMethod: A_MEAN, S_FULL, S_PSMN, S_MEAN, C_MEAN, C_PARA</t>
+          <t>EPMethod: A_MEAN, S_FULL, S_PSMN, S_MEAN, C_MEAN</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="G124" s="38" t="inlineStr">
         <is>
-          <t>String code for EP calculation method (ORD v2): A_MEAN, S_FULL, S_PSMN, S_MEAN, C_MEAN, C_PARA. Prefix indicates LossMethod (A_=MEAN, S_=STOC, C_=CONV).</t>
+          <t>String code for EP calculation method (ORD v2): A_MEAN, S_FULL, S_PSMN, S_MEAN, C_MEAN. Prefix indicates LossMethod (A_=MEAN, S_=STOC, C_=CONV).</t>
         </is>
       </c>
       <c r="H124" s="38" t="inlineStr">

--- a/Docs/ORD_Data_Spec.xlsx
+++ b/Docs/ORD_Data_Spec.xlsx
@@ -1539,7 +1539,7 @@
       </c>
       <c r="H11" s="75" t="inlineStr">
         <is>
-          <t>SourceExposure, SourceNumLocs</t>
+          <t>SourceExposure, SourceNumLocs, LossMethod (ORD v2)</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z19"/>
+  <dimension ref="A1:AI19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col width="21.1640625" customWidth="1" style="111" min="1" max="1"/>
@@ -4952,6 +4952,18 @@
     <col width="16.6640625" customWidth="1" style="111" min="16" max="16"/>
     <col width="12" customWidth="1" style="111" min="17" max="17"/>
     <col width="11.5" customWidth="1" style="111" min="18" max="16384"/>
+    <col width="13" customWidth="1" style="61" min="24" max="24"/>
+    <col width="13" customWidth="1" style="61" min="25" max="25"/>
+    <col width="13" customWidth="1" style="61" min="26" max="26"/>
+    <col width="13" customWidth="1" style="61" min="28" max="28"/>
+    <col width="13" customWidth="1" style="61" min="29" max="29"/>
+    <col width="13" customWidth="1" style="61" min="30" max="30"/>
+    <col width="13" customWidth="1" style="61" min="31" max="31"/>
+    <col width="13" customWidth="1" style="61" min="32" max="32"/>
+    <col width="13" customWidth="1" style="61" min="33" max="33"/>
+    <col width="13" customWidth="1" style="61" min="34" max="34"/>
+    <col width="13" customWidth="1" style="61" min="35" max="35"/>
+    <col width="13" customWidth="1" style="61" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5000,6 +5012,21 @@
           <t>PSEPT</t>
         </is>
       </c>
+      <c r="AB1" s="113" t="inlineStr">
+        <is>
+          <t>GPLT</t>
+        </is>
+      </c>
+      <c r="AE1" s="113" t="inlineStr">
+        <is>
+          <t>GALT</t>
+        </is>
+      </c>
+      <c r="AH1" s="113" t="inlineStr">
+        <is>
+          <t>GEPT</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="112" t="inlineStr">
@@ -5092,6 +5119,36 @@
           <t>Data Type</t>
         </is>
       </c>
+      <c r="AB2" s="112" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="AC2" s="112" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="AE2" s="112" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="AF2" s="112" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="AH2" s="112" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="AI2" s="112" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="111" t="inlineStr">
@@ -5184,6 +5241,36 @@
           <t>32-bit integer</t>
         </is>
       </c>
+      <c r="AB3" s="111" t="inlineStr">
+        <is>
+          <t>GroupEventSetId</t>
+        </is>
+      </c>
+      <c r="AC3" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE3" s="111" t="inlineStr">
+        <is>
+          <t>GroupEventSetId</t>
+        </is>
+      </c>
+      <c r="AF3" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AH3" s="111" t="inlineStr">
+        <is>
+          <t>GroupEventSetId</t>
+        </is>
+      </c>
+      <c r="AI3" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="111" t="inlineStr">
@@ -5248,30 +5335,60 @@
       </c>
       <c r="S4" s="111" t="inlineStr">
         <is>
-          <t>SampleType</t>
+          <t>LossMethod</t>
         </is>
       </c>
       <c r="T4" s="111" t="inlineStr">
         <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="V4" s="111" t="inlineStr">
+        <is>
+          <t>EPMethod</t>
+        </is>
+      </c>
+      <c r="W4" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="Y4" s="111" t="inlineStr">
+        <is>
+          <t>SampleId</t>
+        </is>
+      </c>
+      <c r="Z4" s="111" t="inlineStr">
+        <is>
           <t>32-bit integer</t>
         </is>
       </c>
-      <c r="V4" s="111" t="inlineStr">
-        <is>
-          <t>EPMethod</t>
-        </is>
-      </c>
-      <c r="W4" s="111" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="Y4" s="111" t="inlineStr">
-        <is>
-          <t>SampleId</t>
-        </is>
-      </c>
-      <c r="Z4" s="111" t="inlineStr">
+      <c r="AB4" s="111" t="inlineStr">
+        <is>
+          <t>SummaryId</t>
+        </is>
+      </c>
+      <c r="AC4" s="111" t="inlineStr">
+        <is>
+          <t>32-bit integer</t>
+        </is>
+      </c>
+      <c r="AE4" s="111" t="inlineStr">
+        <is>
+          <t>SummaryId</t>
+        </is>
+      </c>
+      <c r="AF4" s="111" t="inlineStr">
+        <is>
+          <t>32-bit integer</t>
+        </is>
+      </c>
+      <c r="AH4" s="111" t="inlineStr">
+        <is>
+          <t>SummaryId</t>
+        </is>
+      </c>
+      <c r="AI4" s="111" t="inlineStr">
         <is>
           <t>32-bit integer</t>
         </is>
@@ -5340,12 +5457,12 @@
       </c>
       <c r="S5" s="111" t="inlineStr">
         <is>
-          <t>MeanLoss</t>
+          <t>SampleType</t>
         </is>
       </c>
       <c r="T5" s="111" t="inlineStr">
         <is>
-          <t>float</t>
+          <t>32-bit integer</t>
         </is>
       </c>
       <c r="V5" s="111" t="inlineStr">
@@ -5364,6 +5481,36 @@
         </is>
       </c>
       <c r="Z5" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AB5" s="111" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="AC5" s="111" t="inlineStr">
+        <is>
+          <t>32-bit integer</t>
+        </is>
+      </c>
+      <c r="AE5" s="111" t="inlineStr">
+        <is>
+          <t>GroupMethod</t>
+        </is>
+      </c>
+      <c r="AF5" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AH5" s="111" t="inlineStr">
+        <is>
+          <t>GroupMethod</t>
+        </is>
+      </c>
+      <c r="AI5" s="111" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -5432,7 +5579,7 @@
       </c>
       <c r="S6" s="111" t="inlineStr">
         <is>
-          <t>SDLoss</t>
+          <t>MeanLoss</t>
         </is>
       </c>
       <c r="T6" s="111" t="inlineStr">
@@ -5456,6 +5603,36 @@
         </is>
       </c>
       <c r="Z6" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB6" s="111" t="inlineStr">
+        <is>
+          <t>EventId</t>
+        </is>
+      </c>
+      <c r="AC6" s="111" t="inlineStr">
+        <is>
+          <t>32-bit integer</t>
+        </is>
+      </c>
+      <c r="AE6" s="111" t="inlineStr">
+        <is>
+          <t>MeanLoss</t>
+        </is>
+      </c>
+      <c r="AF6" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH6" s="111" t="inlineStr">
+        <is>
+          <t>ReturnPeriod</t>
+        </is>
+      </c>
+      <c r="AI6" s="111" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -5512,6 +5689,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="S7" s="111" t="inlineStr">
+        <is>
+          <t>SDLoss</t>
+        </is>
+      </c>
+      <c r="T7" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="V7" s="111" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -5528,6 +5715,36 @@
         </is>
       </c>
       <c r="Z7" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AB7" s="111" t="inlineStr">
+        <is>
+          <t>GroupMethod</t>
+        </is>
+      </c>
+      <c r="AC7" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="AE7" s="111" t="inlineStr">
+        <is>
+          <t>SDLoss</t>
+        </is>
+      </c>
+      <c r="AF7" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="AH7" s="111" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="AI7" s="111" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -5574,6 +5791,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AB8" s="111" t="inlineStr">
+        <is>
+          <t>Loss</t>
+        </is>
+      </c>
+      <c r="AC8" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="111" t="inlineStr">
@@ -5868,14 +6095,17 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
+    <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="S1:T1"/>
+    <mergeCell ref="AH1:AI1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="P1:Q1"/>
+    <mergeCell ref="AE1:AF1"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="M1:N1"/>
   </mergeCells>
@@ -5899,7 +6129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I157"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -5994,7 +6224,7 @@
       </c>
       <c r="C8" s="76" t="inlineStr">
         <is>
-          <t>ALT,EPT,PSEPT,MELT,MPLT,SELT,SPLT,QELT,QPLT</t>
+          <t>ALT,EPT,PSEPT,MELT,MPLT,SELT,SPLT,QELT,QPLT,GPLT,GALT,GEPT</t>
         </is>
       </c>
       <c r="D8" s="76" t="inlineStr">
@@ -6064,7 +6294,7 @@
       </c>
       <c r="C10" s="76" t="inlineStr">
         <is>
-          <t>ALT,MELT,MPLT</t>
+          <t>ALT,MELT,MPLT,GALT</t>
         </is>
       </c>
       <c r="D10" s="76" t="inlineStr">
@@ -6097,7 +6327,7 @@
       </c>
       <c r="C11" s="76" t="inlineStr">
         <is>
-          <t>ALT,MELT,MPLT</t>
+          <t>ALT,MELT,MPLT,GALT</t>
         </is>
       </c>
       <c r="D11" s="76" t="inlineStr">
@@ -6266,7 +6496,7 @@
       </c>
       <c r="C16" s="76" t="inlineStr">
         <is>
-          <t>EPT, PSEPT</t>
+          <t>EPT, PSEPT, GEPT</t>
         </is>
       </c>
       <c r="D16" s="76" t="inlineStr">
@@ -6299,7 +6529,7 @@
       </c>
       <c r="C17" s="76" t="inlineStr">
         <is>
-          <t>EPT,PSEPT,SELT,SPLT,QELT,QPLT</t>
+          <t>EPT,PSEPT,SELT,SPLT,QELT,QPLT,GPLT,GEPT</t>
         </is>
       </c>
       <c r="D17" s="76" t="inlineStr">
@@ -6369,7 +6599,7 @@
       </c>
       <c r="C19" s="76" t="inlineStr">
         <is>
-          <t>MELT,MPLT,SELT,SPLT,QELT,QPLT</t>
+          <t>MELT,MPLT,SELT,SPLT,QELT,QPLT,GPLT</t>
         </is>
       </c>
       <c r="D19" s="76" t="inlineStr">
@@ -6402,7 +6632,7 @@
       </c>
       <c r="C20" s="76" t="inlineStr">
         <is>
-          <t>MPLT,QPLT,SPLT</t>
+          <t>MPLT,QPLT,SPLT,GPLT</t>
         </is>
       </c>
       <c r="D20" s="76" t="inlineStr">
@@ -10131,7 +10361,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ALT,GALT</t>
+          <t>ALT</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10198,7 +10428,41 @@
       </c>
     </row>
     <row r="127">
-      <c r="H127" s="38" t="n"/>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>GPLT,GALT,GEPT</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>GroupEventSetId</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Identifier of the GroupEventSet: the set of analyses with compatible event sets that were combined in the grouped analysis. Opaque string whose structure is platform-specific; compare it as a whole and never parse it.</t>
+        </is>
+      </c>
+      <c r="H127" s="38" t="inlineStr">
+        <is>
+          <t>New in ORD v2</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="H128" s="38" t="n"/>

--- a/Docs/ORD_Data_Spec.xlsx
+++ b/Docs/ORD_Data_Spec.xlsx
@@ -1574,7 +1574,11 @@
           <t>OEP</t>
         </is>
       </c>
-      <c r="H12" s="30" t="n"/>
+      <c r="H12" s="75" t="inlineStr">
+        <is>
+          <t>SDLoss, MaxLoss (optional, ORD v2)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="50.75" customHeight="1" s="61">
       <c r="B13" s="35" t="inlineStr">
@@ -2239,7 +2243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:DM53"/>
+  <dimension ref="B1:DO53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -2296,27 +2300,29 @@
     <col width="12.33203125" customWidth="1" style="61" min="88" max="89"/>
     <col width="12.6640625" customWidth="1" style="61" min="90" max="90"/>
     <col width="10.5" customWidth="1" style="61" min="91" max="91"/>
-    <col width="2.6640625" customWidth="1" style="61" min="92" max="92"/>
-    <col width="14.5" customWidth="1" style="61" min="93" max="94"/>
-    <col width="10.6640625" customWidth="1" style="61" min="95" max="95"/>
-    <col width="13.6640625" customWidth="1" style="61" min="96" max="96"/>
-    <col width="12" customWidth="1" style="61" min="97" max="97"/>
-    <col width="2.6640625" customWidth="1" style="61" min="98" max="98"/>
-    <col width="12.5" customWidth="1" style="61" min="99" max="99"/>
-    <col width="11.5" customWidth="1" style="61" min="100" max="100"/>
-    <col width="14" customWidth="1" style="61" min="101" max="101"/>
-    <col width="9.33203125" customWidth="1" style="61" min="103" max="103"/>
-    <col width="12.5" customWidth="1" style="61" min="104" max="104"/>
-    <col width="2.6640625" customWidth="1" style="61" min="105" max="105"/>
-    <col width="13.6640625" customWidth="1" style="61" min="106" max="108"/>
-    <col width="15.33203125" customWidth="1" style="61" min="109" max="110"/>
-    <col width="17.5" customWidth="1" style="61" min="111" max="111"/>
-    <col width="17.6640625" customWidth="1" style="61" min="112" max="112"/>
-    <col width="2.6640625" customWidth="1" style="61" min="113" max="113"/>
-    <col width="14.33203125" customWidth="1" style="61" min="114" max="114"/>
-    <col width="24.83203125" customWidth="1" style="61" min="115" max="115"/>
-    <col width="14.6640625" customWidth="1" style="61" min="116" max="116"/>
-    <col width="14.5" customWidth="1" style="61" min="117" max="117"/>
+    <col width="10.5" customWidth="1" style="61" min="92" max="92"/>
+    <col width="10.5" customWidth="1" style="61" min="93" max="93"/>
+    <col width="2.6640625" customWidth="1" style="61" min="94" max="94"/>
+    <col width="14.5" customWidth="1" style="61" min="95" max="95"/>
+    <col width="10.6640625" customWidth="1" style="61" min="97" max="97"/>
+    <col width="13.6640625" customWidth="1" style="61" min="98" max="98"/>
+    <col width="12" customWidth="1" style="61" min="99" max="99"/>
+    <col width="2.6640625" customWidth="1" style="61" min="100" max="100"/>
+    <col width="12.5" customWidth="1" style="61" min="101" max="101"/>
+    <col width="11.5" customWidth="1" style="61" min="102" max="102"/>
+    <col width="14" customWidth="1" style="61" min="103" max="103"/>
+    <col width="9.33203125" customWidth="1" style="61" min="105" max="105"/>
+    <col width="12.5" customWidth="1" style="61" min="106" max="106"/>
+    <col width="2.6640625" customWidth="1" style="61" min="107" max="107"/>
+    <col width="13.6640625" customWidth="1" style="61" min="108" max="108"/>
+    <col width="15.33203125" customWidth="1" style="61" min="111" max="111"/>
+    <col width="17.5" customWidth="1" style="61" min="113" max="113"/>
+    <col width="17.6640625" customWidth="1" style="61" min="114" max="114"/>
+    <col width="2.6640625" customWidth="1" style="61" min="115" max="115"/>
+    <col width="14.33203125" customWidth="1" style="61" min="116" max="116"/>
+    <col width="24.83203125" customWidth="1" style="61" min="117" max="117"/>
+    <col width="14.6640625" customWidth="1" style="61" min="118" max="118"/>
+    <col width="14.5" customWidth="1" style="61" min="119" max="119"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1" s="61">
@@ -2336,15 +2342,19 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="86" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="86" t="n"/>
     </row>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9">
       <c r="CI9" s="86" t="n"/>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="66" t="inlineStr">
         <is>
@@ -2415,23 +2425,23 @@
           <t>Exceedance Probability Table (EPT)</t>
         </is>
       </c>
-      <c r="CO11" s="66" t="inlineStr">
+      <c r="CQ11" s="66" t="inlineStr">
         <is>
           <t>Per Sample Exceedance Probability Table (PSEPT)</t>
         </is>
       </c>
-      <c r="CP11" s="66" t="n"/>
-      <c r="CU11" s="66" t="inlineStr">
+      <c r="CR11" s="66" t="n"/>
+      <c r="CW11" s="66" t="inlineStr">
         <is>
           <t>Error Log (ELOG)</t>
         </is>
       </c>
-      <c r="DB11" s="66" t="inlineStr">
+      <c r="DD11" s="66" t="inlineStr">
         <is>
           <t>Aggregate exposure within model domain (DOMEXP)</t>
         </is>
       </c>
-      <c r="DJ11" s="66" t="inlineStr">
+      <c r="DL11" s="66" t="inlineStr">
         <is>
           <t>Aggregate exposure rejected (REJEXP)</t>
         </is>
@@ -2480,7 +2490,7 @@
           <t>EPMethod: A_MEAN, S_FULL, S_PSMN, S_MEAN, C_MEAN</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>EPType: OEP, AEP, TVAR_OEP, TVAR_AEP</t>
         </is>
@@ -2553,9 +2563,9 @@
           <t>EPType: OEP, AEP, TVAR_OEP, TVAR_AEP</t>
         </is>
       </c>
-      <c r="DC13" s="86" t="n"/>
       <c r="DE13" s="86" t="n"/>
-      <c r="DL13" s="86" t="n"/>
+      <c r="DG13" s="86" t="n"/>
+      <c r="DN13" s="86" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="47" t="inlineStr">
@@ -2600,32 +2610,32 @@
           <t>Existing amended table</t>
         </is>
       </c>
-      <c r="CO14" s="47" t="inlineStr">
+      <c r="CQ14" s="47" t="inlineStr">
         <is>
           <t>Existing amended table</t>
         </is>
       </c>
-      <c r="CU14" s="47" t="inlineStr">
+      <c r="CW14" s="47" t="inlineStr">
         <is>
           <t>Existing amended table</t>
         </is>
       </c>
-      <c r="DB14" s="47" t="inlineStr">
+      <c r="DD14" s="47" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="DC14" s="86" t="n"/>
-      <c r="DD14" s="86" t="n"/>
       <c r="DE14" s="86" t="n"/>
       <c r="DF14" s="86" t="n"/>
-      <c r="DJ14" s="47" t="inlineStr">
+      <c r="DG14" s="86" t="n"/>
+      <c r="DH14" s="86" t="n"/>
+      <c r="DL14" s="47" t="inlineStr">
         <is>
           <t>New</t>
         </is>
       </c>
-      <c r="DL14" s="86" t="n"/>
-      <c r="DM14" s="86" t="n"/>
+      <c r="DN14" s="86" t="n"/>
+      <c r="DO14" s="86" t="n"/>
     </row>
     <row r="15">
       <c r="B15" s="48" t="inlineStr">
@@ -3038,117 +3048,127 @@
           <t>ReturnPeriod</t>
         </is>
       </c>
-      <c r="CM15" s="50" t="inlineStr">
+      <c r="CM15" s="49" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="CO15" s="48" t="inlineStr">
+      <c r="CN15" s="49" t="inlineStr">
+        <is>
+          <t>SDLoss</t>
+        </is>
+      </c>
+      <c r="CO15" s="50" t="inlineStr">
+        <is>
+          <t>MaxLoss</t>
+        </is>
+      </c>
+      <c r="CQ15" s="48" t="inlineStr">
         <is>
           <t>SummaryId</t>
         </is>
       </c>
-      <c r="CP15" s="49" t="inlineStr">
+      <c r="CR15" s="49" t="inlineStr">
         <is>
           <t>SampleId</t>
         </is>
       </c>
-      <c r="CQ15" s="49" t="inlineStr">
+      <c r="CS15" s="49" t="inlineStr">
         <is>
           <t>EPType</t>
         </is>
       </c>
-      <c r="CR15" s="49" t="inlineStr">
+      <c r="CT15" s="49" t="inlineStr">
         <is>
           <t>ReturnPeriod</t>
         </is>
       </c>
-      <c r="CS15" s="50" t="inlineStr">
+      <c r="CU15" s="50" t="inlineStr">
         <is>
           <t>Loss</t>
         </is>
       </c>
-      <c r="CU15" s="48" t="inlineStr">
+      <c r="CW15" s="48" t="inlineStr">
         <is>
           <t>PortNumber</t>
         </is>
       </c>
-      <c r="CV15" s="49" t="inlineStr">
+      <c r="CX15" s="49" t="inlineStr">
         <is>
           <t>AccNumber</t>
         </is>
       </c>
-      <c r="CW15" s="49" t="inlineStr">
+      <c r="CY15" s="49" t="inlineStr">
         <is>
           <t>LocNumber</t>
         </is>
       </c>
-      <c r="CX15" s="49" t="inlineStr">
+      <c r="CZ15" s="49" t="inlineStr">
         <is>
           <t>Coverage</t>
         </is>
       </c>
-      <c r="CY15" s="49" t="inlineStr">
+      <c r="DA15" s="49" t="inlineStr">
         <is>
           <t>PerilCode</t>
         </is>
       </c>
-      <c r="CZ15" s="50" t="inlineStr">
+      <c r="DB15" s="50" t="inlineStr">
         <is>
           <t>ErrorMessage</t>
         </is>
       </c>
-      <c r="DB15" s="48" t="inlineStr">
+      <c r="DD15" s="48" t="inlineStr">
         <is>
           <t>SummaryId</t>
         </is>
       </c>
-      <c r="DC15" s="51" t="inlineStr">
+      <c r="DE15" s="51" t="inlineStr">
         <is>
           <t>SourceExposure</t>
         </is>
       </c>
-      <c r="DD15" s="51" t="inlineStr">
+      <c r="DF15" s="51" t="inlineStr">
         <is>
           <t>SourceNumLocs</t>
         </is>
       </c>
-      <c r="DE15" s="51" t="inlineStr">
+      <c r="DG15" s="51" t="inlineStr">
         <is>
           <t>DomainExposure</t>
         </is>
       </c>
-      <c r="DF15" s="51" t="inlineStr">
+      <c r="DH15" s="51" t="inlineStr">
         <is>
           <t>DomainNumLocs</t>
         </is>
       </c>
-      <c r="DG15" s="49" t="inlineStr">
+      <c r="DI15" s="49" t="inlineStr">
         <is>
           <t>SecModExposure</t>
         </is>
       </c>
-      <c r="DH15" s="50" t="inlineStr">
+      <c r="DJ15" s="50" t="inlineStr">
         <is>
           <t>SecModNumLocs</t>
         </is>
       </c>
-      <c r="DJ15" s="48" t="inlineStr">
+      <c r="DL15" s="48" t="inlineStr">
         <is>
           <t>SummaryId</t>
         </is>
       </c>
-      <c r="DK15" s="49" t="inlineStr">
+      <c r="DM15" s="49" t="inlineStr">
         <is>
           <t>ErrorMessage</t>
         </is>
       </c>
-      <c r="DL15" s="51" t="inlineStr">
+      <c r="DN15" s="51" t="inlineStr">
         <is>
           <t>SourceExposure</t>
         </is>
       </c>
-      <c r="DM15" s="52" t="inlineStr">
+      <c r="DO15" s="52" t="inlineStr">
         <is>
           <t>SourceNumLocs</t>
         </is>
@@ -3271,37 +3291,39 @@
       <c r="CL16" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="CM16" s="55" t="n"/>
-      <c r="CO16" s="59" t="n">
+      <c r="CM16" s="54" t="n"/>
+      <c r="CN16" s="54" t="n"/>
+      <c r="CO16" s="55" t="n"/>
+      <c r="CQ16" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP16" s="54" t="n">
+      <c r="CR16" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CQ16" s="54" t="inlineStr">
+      <c r="CS16" s="54" t="inlineStr">
         <is>
           <t>OEP</t>
         </is>
       </c>
-      <c r="CR16" s="54" t="n">
+      <c r="CT16" s="54" t="n">
         <v>10</v>
       </c>
-      <c r="CS16" s="55" t="n"/>
-      <c r="CU16" s="56" t="n"/>
-      <c r="CZ16" s="58" t="n"/>
-      <c r="DB16" s="59" t="n">
+      <c r="CU16" s="55" t="n"/>
+      <c r="CW16" s="56" t="n"/>
+      <c r="DB16" s="58" t="n"/>
+      <c r="DD16" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="DH16" s="58" t="n"/>
-      <c r="DJ16" s="59" t="n">
+      <c r="DJ16" s="58" t="n"/>
+      <c r="DL16" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="DK16" t="inlineStr">
+      <c r="DM16" t="inlineStr">
         <is>
           <t>ValidAreaPerilInvalidVuln</t>
         </is>
       </c>
-      <c r="DM16" s="58" t="n"/>
+      <c r="DO16" s="58" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="59" t="n">
@@ -3416,35 +3438,37 @@
       <c r="CL17" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="CM17" s="55" t="n"/>
-      <c r="CO17" s="59" t="n">
+      <c r="CM17" s="54" t="n"/>
+      <c r="CN17" s="54" t="n"/>
+      <c r="CO17" s="55" t="n"/>
+      <c r="CQ17" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP17" s="54" t="n">
+      <c r="CR17" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CQ17" s="54" t="n">
+      <c r="CS17" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR17" s="54" t="n">
+      <c r="CT17" s="54" t="n">
         <v>20</v>
       </c>
-      <c r="CS17" s="55" t="n"/>
-      <c r="CU17" s="56" t="n"/>
-      <c r="CZ17" s="58" t="n"/>
-      <c r="DB17" s="59" t="n">
+      <c r="CU17" s="55" t="n"/>
+      <c r="CW17" s="56" t="n"/>
+      <c r="DB17" s="58" t="n"/>
+      <c r="DD17" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="DH17" s="58" t="n"/>
-      <c r="DJ17" s="59" t="n">
+      <c r="DJ17" s="58" t="n"/>
+      <c r="DL17" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="DK17" t="inlineStr">
+      <c r="DM17" t="inlineStr">
         <is>
           <t>InvalidAreaPerilValidVuln</t>
         </is>
       </c>
-      <c r="DM17" s="58" t="n"/>
+      <c r="DO17" s="58" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="59" t="n">
@@ -3559,35 +3583,37 @@
       <c r="CL18" s="54" t="n">
         <v>50</v>
       </c>
-      <c r="CM18" s="55" t="n"/>
-      <c r="CO18" s="59" t="n">
+      <c r="CM18" s="54" t="n"/>
+      <c r="CN18" s="54" t="n"/>
+      <c r="CO18" s="55" t="n"/>
+      <c r="CQ18" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP18" s="54" t="n">
+      <c r="CR18" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CQ18" s="54" t="n">
+      <c r="CS18" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR18" s="54" t="n">
+      <c r="CT18" s="54" t="n">
         <v>50</v>
       </c>
-      <c r="CS18" s="55" t="n"/>
-      <c r="CU18" s="56" t="n"/>
-      <c r="CZ18" s="58" t="n"/>
-      <c r="DB18" s="59" t="n">
+      <c r="CU18" s="55" t="n"/>
+      <c r="CW18" s="56" t="n"/>
+      <c r="DB18" s="58" t="n"/>
+      <c r="DD18" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="DH18" s="58" t="n"/>
-      <c r="DJ18" s="59" t="n">
+      <c r="DJ18" s="58" t="n"/>
+      <c r="DL18" s="59" t="n">
         <v>1</v>
       </c>
-      <c r="DK18" t="inlineStr">
+      <c r="DM18" t="inlineStr">
         <is>
           <t>InvalidAreaPerilInvalidVuln</t>
         </is>
       </c>
-      <c r="DM18" s="58" t="n"/>
+      <c r="DO18" s="58" t="n"/>
     </row>
     <row r="19">
       <c r="B19" s="59" t="n">
@@ -3671,33 +3697,35 @@
       <c r="CL19" s="54" t="n">
         <v>100</v>
       </c>
-      <c r="CM19" s="55" t="n"/>
-      <c r="CO19" s="59" t="n">
+      <c r="CM19" s="54" t="n"/>
+      <c r="CN19" s="54" t="n"/>
+      <c r="CO19" s="55" t="n"/>
+      <c r="CQ19" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP19" s="54" t="n">
+      <c r="CR19" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CQ19" s="54" t="n">
+      <c r="CS19" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR19" s="54" t="n">
+      <c r="CT19" s="54" t="n">
         <v>100</v>
       </c>
-      <c r="CS19" s="55" t="n"/>
-      <c r="CU19" s="56" t="n"/>
-      <c r="CZ19" s="58" t="n"/>
-      <c r="DB19" s="59" t="n"/>
-      <c r="DH19" s="58" t="n"/>
-      <c r="DJ19" s="59" t="n">
+      <c r="CU19" s="55" t="n"/>
+      <c r="CW19" s="56" t="n"/>
+      <c r="DB19" s="58" t="n"/>
+      <c r="DD19" s="59" t="n"/>
+      <c r="DJ19" s="58" t="n"/>
+      <c r="DL19" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="DK19" t="inlineStr">
+      <c r="DM19" t="inlineStr">
         <is>
           <t>ValidAreaPerilInvalidVuln</t>
         </is>
       </c>
-      <c r="DM19" s="58" t="n"/>
+      <c r="DO19" s="58" t="n"/>
     </row>
     <row r="20">
       <c r="B20" s="59" t="n">
@@ -3781,33 +3809,35 @@
       <c r="CL20" s="54" t="n">
         <v>1000</v>
       </c>
-      <c r="CM20" s="55" t="n"/>
-      <c r="CO20" s="59" t="n">
+      <c r="CM20" s="54" t="n"/>
+      <c r="CN20" s="54" t="n"/>
+      <c r="CO20" s="55" t="n"/>
+      <c r="CQ20" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP20" s="54" t="n">
+      <c r="CR20" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CQ20" s="54" t="n">
+      <c r="CS20" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR20" s="54" t="n">
+      <c r="CT20" s="54" t="n">
         <v>1000</v>
       </c>
-      <c r="CS20" s="55" t="n"/>
-      <c r="CU20" s="56" t="n"/>
-      <c r="CZ20" s="58" t="n"/>
-      <c r="DB20" s="59" t="n"/>
-      <c r="DH20" s="58" t="n"/>
-      <c r="DJ20" s="59" t="n">
+      <c r="CU20" s="55" t="n"/>
+      <c r="CW20" s="56" t="n"/>
+      <c r="DB20" s="58" t="n"/>
+      <c r="DD20" s="59" t="n"/>
+      <c r="DJ20" s="58" t="n"/>
+      <c r="DL20" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="DK20" t="inlineStr">
+      <c r="DM20" t="inlineStr">
         <is>
           <t>InvalidAreaPerilValidVuln</t>
         </is>
       </c>
-      <c r="DM20" s="58" t="n"/>
+      <c r="DO20" s="58" t="n"/>
     </row>
     <row r="21">
       <c r="B21" s="59" t="n">
@@ -3874,31 +3904,33 @@
         <v>2</v>
       </c>
       <c r="CL21" s="54" t="n"/>
-      <c r="CM21" s="55" t="n"/>
-      <c r="CO21" s="59" t="n">
+      <c r="CM21" s="54" t="n"/>
+      <c r="CN21" s="54" t="n"/>
+      <c r="CO21" s="55" t="n"/>
+      <c r="CQ21" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP21" s="54" t="n">
+      <c r="CR21" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="CQ21" s="54" t="n">
+      <c r="CS21" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR21" s="54" t="n"/>
-      <c r="CS21" s="55" t="n"/>
-      <c r="CU21" s="56" t="n"/>
-      <c r="CZ21" s="58" t="n"/>
-      <c r="DB21" s="56" t="n"/>
-      <c r="DH21" s="58" t="n"/>
-      <c r="DJ21" s="59" t="n">
+      <c r="CT21" s="54" t="n"/>
+      <c r="CU21" s="55" t="n"/>
+      <c r="CW21" s="56" t="n"/>
+      <c r="DB21" s="58" t="n"/>
+      <c r="DD21" s="56" t="n"/>
+      <c r="DJ21" s="58" t="n"/>
+      <c r="DL21" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="DK21" t="inlineStr">
+      <c r="DM21" t="inlineStr">
         <is>
           <t>InvalidAreaPerilInvalidVuln</t>
         </is>
       </c>
-      <c r="DM21" s="58" t="n"/>
+      <c r="DO21" s="58" t="n"/>
     </row>
     <row r="22">
       <c r="B22" s="59" t="n">
@@ -3965,31 +3997,33 @@
         <v>2</v>
       </c>
       <c r="CL22" s="54" t="n"/>
-      <c r="CM22" s="55" t="n"/>
-      <c r="CO22" s="59" t="n">
+      <c r="CM22" s="54" t="n"/>
+      <c r="CN22" s="54" t="n"/>
+      <c r="CO22" s="55" t="n"/>
+      <c r="CQ22" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP22" s="54" t="n">
+      <c r="CR22" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="CQ22" s="54" t="n">
+      <c r="CS22" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR22" s="54" t="n"/>
-      <c r="CS22" s="55" t="n"/>
-      <c r="CU22" s="56" t="n"/>
-      <c r="CZ22" s="58" t="n"/>
-      <c r="DB22" s="56" t="n"/>
-      <c r="DH22" s="58" t="n"/>
-      <c r="DJ22" s="59" t="n">
+      <c r="CT22" s="54" t="n"/>
+      <c r="CU22" s="55" t="n"/>
+      <c r="CW22" s="56" t="n"/>
+      <c r="DB22" s="58" t="n"/>
+      <c r="DD22" s="56" t="n"/>
+      <c r="DJ22" s="58" t="n"/>
+      <c r="DL22" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="DK22" t="inlineStr">
+      <c r="DM22" t="inlineStr">
         <is>
           <t>ValidAreaPerilInvalidVuln</t>
         </is>
       </c>
-      <c r="DM22" s="58" t="n"/>
+      <c r="DO22" s="58" t="n"/>
     </row>
     <row r="23">
       <c r="B23" s="59" t="n">
@@ -4056,31 +4090,33 @@
         <v>2</v>
       </c>
       <c r="CL23" s="54" t="n"/>
-      <c r="CM23" s="55" t="n"/>
-      <c r="CO23" s="59" t="n">
+      <c r="CM23" s="54" t="n"/>
+      <c r="CN23" s="54" t="n"/>
+      <c r="CO23" s="55" t="n"/>
+      <c r="CQ23" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="CP23" s="54" t="n">
+      <c r="CR23" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="CQ23" s="54" t="n">
+      <c r="CS23" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR23" s="54" t="n"/>
-      <c r="CS23" s="55" t="n"/>
-      <c r="CU23" s="56" t="n"/>
-      <c r="CZ23" s="58" t="n"/>
-      <c r="DB23" s="56" t="n"/>
-      <c r="DH23" s="58" t="n"/>
-      <c r="DJ23" s="59" t="n">
+      <c r="CT23" s="54" t="n"/>
+      <c r="CU23" s="55" t="n"/>
+      <c r="CW23" s="56" t="n"/>
+      <c r="DB23" s="58" t="n"/>
+      <c r="DD23" s="56" t="n"/>
+      <c r="DJ23" s="58" t="n"/>
+      <c r="DL23" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="DK23" t="inlineStr">
+      <c r="DM23" t="inlineStr">
         <is>
           <t>InvalidAreaPerilValidVuln</t>
         </is>
       </c>
-      <c r="DM23" s="58" t="n"/>
+      <c r="DO23" s="58" t="n"/>
     </row>
     <row r="24">
       <c r="B24" s="59" t="n">
@@ -4147,31 +4183,33 @@
         <v>2</v>
       </c>
       <c r="CL24" s="54" t="n"/>
-      <c r="CM24" s="55" t="n"/>
-      <c r="CO24" s="59" t="n">
+      <c r="CM24" s="54" t="n"/>
+      <c r="CN24" s="54" t="n"/>
+      <c r="CO24" s="55" t="n"/>
+      <c r="CQ24" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="CP24" s="54" t="n">
+      <c r="CR24" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="CQ24" s="54" t="n">
+      <c r="CS24" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR24" s="54" t="n"/>
-      <c r="CS24" s="55" t="n"/>
-      <c r="CU24" s="56" t="n"/>
-      <c r="CZ24" s="58" t="n"/>
-      <c r="DB24" s="56" t="n"/>
-      <c r="DH24" s="58" t="n"/>
-      <c r="DJ24" s="59" t="n">
+      <c r="CT24" s="54" t="n"/>
+      <c r="CU24" s="55" t="n"/>
+      <c r="CW24" s="56" t="n"/>
+      <c r="DB24" s="58" t="n"/>
+      <c r="DD24" s="56" t="n"/>
+      <c r="DJ24" s="58" t="n"/>
+      <c r="DL24" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="DK24" t="inlineStr">
+      <c r="DM24" t="inlineStr">
         <is>
           <t>InvalidAreaPerilInvalidVuln</t>
         </is>
       </c>
-      <c r="DM24" s="58" t="n"/>
+      <c r="DO24" s="58" t="n"/>
     </row>
     <row r="25">
       <c r="B25" s="59" t="n">
@@ -4238,26 +4276,28 @@
         <v>2</v>
       </c>
       <c r="CL25" s="54" t="n"/>
-      <c r="CM25" s="55" t="n"/>
-      <c r="CO25" s="59" t="n">
+      <c r="CM25" s="54" t="n"/>
+      <c r="CN25" s="54" t="n"/>
+      <c r="CO25" s="55" t="n"/>
+      <c r="CQ25" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="CP25" s="54" t="n">
+      <c r="CR25" s="54" t="n">
         <v>2</v>
       </c>
-      <c r="CQ25" s="54" t="n">
+      <c r="CS25" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR25" s="54" t="n"/>
-      <c r="CS25" s="55" t="n"/>
-      <c r="CU25" s="56" t="n"/>
-      <c r="CZ25" s="58" t="n"/>
-      <c r="DB25" s="56" t="n"/>
-      <c r="DH25" s="58" t="n"/>
-      <c r="DJ25" s="59" t="n">
+      <c r="CT25" s="54" t="n"/>
+      <c r="CU25" s="55" t="n"/>
+      <c r="CW25" s="56" t="n"/>
+      <c r="DB25" s="58" t="n"/>
+      <c r="DD25" s="56" t="n"/>
+      <c r="DJ25" s="58" t="n"/>
+      <c r="DL25" s="59" t="n">
         <v>3</v>
       </c>
-      <c r="DK25" t="inlineStr">
+      <c r="DM25" t="inlineStr">
         <is>
           <t>Invalid lat-long</t>
         </is>
@@ -4328,22 +4368,24 @@
         <v>3</v>
       </c>
       <c r="CL26" s="54" t="n"/>
-      <c r="CM26" s="55" t="n"/>
-      <c r="CO26" s="59" t="n">
+      <c r="CM26" s="54" t="n"/>
+      <c r="CN26" s="54" t="n"/>
+      <c r="CO26" s="55" t="n"/>
+      <c r="CQ26" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="CP26" s="54" t="n">
+      <c r="CR26" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="CQ26" s="54" t="n">
+      <c r="CS26" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR26" s="54" t="n"/>
-      <c r="CS26" s="55" t="n"/>
-      <c r="CU26" s="56" t="n"/>
-      <c r="CZ26" s="58" t="n"/>
-      <c r="DB26" s="56" t="n"/>
-      <c r="DH26" s="58" t="n"/>
+      <c r="CT26" s="54" t="n"/>
+      <c r="CU26" s="55" t="n"/>
+      <c r="CW26" s="56" t="n"/>
+      <c r="DB26" s="58" t="n"/>
+      <c r="DD26" s="56" t="n"/>
+      <c r="DJ26" s="58" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="59" t="n">
@@ -4406,20 +4448,22 @@
         <v>3</v>
       </c>
       <c r="CL27" s="54" t="n"/>
-      <c r="CM27" s="58" t="n"/>
-      <c r="CO27" s="59" t="n">
+      <c r="CM27" s="54" t="n"/>
+      <c r="CN27" s="54" t="n"/>
+      <c r="CO27" s="58" t="n"/>
+      <c r="CQ27" s="59" t="n">
         <v>5</v>
       </c>
-      <c r="CP27" s="54" t="n">
+      <c r="CR27" s="54" t="n">
         <v>3</v>
       </c>
-      <c r="CQ27" s="54" t="n">
+      <c r="CS27" s="54" t="n">
         <v>1</v>
       </c>
-      <c r="CR27" s="54" t="n"/>
-      <c r="CS27" s="58" t="n"/>
-      <c r="CU27" s="56" t="n"/>
-      <c r="CZ27" s="58" t="n"/>
+      <c r="CT27" s="54" t="n"/>
+      <c r="CU27" s="58" t="n"/>
+      <c r="CW27" s="56" t="n"/>
+      <c r="DB27" s="58" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="59" t="n">
@@ -4464,7 +4508,7 @@
         <v>0.25</v>
       </c>
       <c r="BC28" s="58" t="n"/>
-      <c r="CP28" s="54" t="n"/>
+      <c r="CR28" s="54" t="n"/>
     </row>
     <row r="29">
       <c r="B29" s="59" t="n">
@@ -4509,7 +4553,7 @@
         <v>0.5</v>
       </c>
       <c r="BC29" s="58" t="n"/>
-      <c r="CP29" s="54" t="n"/>
+      <c r="CR29" s="54" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="59" t="n">
@@ -4554,7 +4598,7 @@
         <v>0.75</v>
       </c>
       <c r="BC30" s="58" t="n"/>
-      <c r="CP30" s="54" t="n"/>
+      <c r="CR30" s="54" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="59" t="n">
@@ -4599,7 +4643,7 @@
         <v>1</v>
       </c>
       <c r="BC31" s="58" t="n"/>
-      <c r="CP31" s="54" t="n"/>
+      <c r="CR31" s="54" t="n"/>
     </row>
     <row r="32">
       <c r="AE32" s="59" t="n">
@@ -4636,7 +4680,7 @@
         <v>0.25</v>
       </c>
       <c r="BC32" s="58" t="n"/>
-      <c r="CP32" s="54" t="n"/>
+      <c r="CR32" s="54" t="n"/>
     </row>
     <row r="33">
       <c r="AE33" s="59" t="n">
@@ -4673,8 +4717,8 @@
         <v>0.5</v>
       </c>
       <c r="BC33" s="58" t="n"/>
-      <c r="CP33" s="54" t="n"/>
-      <c r="DB33" s="86" t="n"/>
+      <c r="CR33" s="54" t="n"/>
+      <c r="DD33" s="86" t="n"/>
     </row>
     <row r="34">
       <c r="AE34" s="59" t="n">
@@ -4711,9 +4755,9 @@
         <v>0.75</v>
       </c>
       <c r="BC34" s="58" t="n"/>
-      <c r="CP34" s="54" t="n"/>
-      <c r="DB34" s="86" t="n"/>
-      <c r="DC34" s="86" t="n"/>
+      <c r="CR34" s="54" t="n"/>
+      <c r="DD34" s="86" t="n"/>
+      <c r="DE34" s="86" t="n"/>
     </row>
     <row r="35">
       <c r="AE35" s="59" t="n">
@@ -4750,9 +4794,9 @@
         <v>1</v>
       </c>
       <c r="BC35" s="58" t="n"/>
-      <c r="CP35" s="54" t="n"/>
-      <c r="DB35" s="86" t="n"/>
-      <c r="DC35" s="86" t="n"/>
+      <c r="CR35" s="54" t="n"/>
+      <c r="DD35" s="86" t="n"/>
+      <c r="DE35" s="86" t="n"/>
     </row>
     <row r="36">
       <c r="AE36" s="59" t="n">
@@ -4772,9 +4816,9 @@
         <v>3</v>
       </c>
       <c r="AQ36" s="58" t="n"/>
-      <c r="CP36" s="54" t="n"/>
-      <c r="DB36" s="86" t="n"/>
-      <c r="DC36" s="86" t="n"/>
+      <c r="CR36" s="54" t="n"/>
+      <c r="DD36" s="86" t="n"/>
+      <c r="DE36" s="86" t="n"/>
     </row>
     <row r="37">
       <c r="AE37" s="59" t="n">
@@ -4794,9 +4838,9 @@
         <v>4</v>
       </c>
       <c r="AQ37" s="58" t="n"/>
-      <c r="CP37" s="54" t="n"/>
-      <c r="DB37" s="86" t="n"/>
-      <c r="DC37" s="86" t="n"/>
+      <c r="CR37" s="54" t="n"/>
+      <c r="DD37" s="86" t="n"/>
+      <c r="DE37" s="86" t="n"/>
     </row>
     <row r="38">
       <c r="AE38" s="59" t="n">
@@ -4816,7 +4860,7 @@
         <v>-1</v>
       </c>
       <c r="AQ38" s="58" t="n"/>
-      <c r="CP38" s="54" t="n"/>
+      <c r="CR38" s="54" t="n"/>
     </row>
     <row r="39">
       <c r="AE39" s="59" t="n">
@@ -4836,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="AQ39" s="58" t="n"/>
-      <c r="CP39" s="54" t="n"/>
+      <c r="CR39" s="54" t="n"/>
     </row>
     <row r="40">
       <c r="AE40" s="59" t="n">
@@ -4856,7 +4900,7 @@
         <v>2</v>
       </c>
       <c r="AQ40" s="58" t="n"/>
-      <c r="CP40" s="54" t="n"/>
+      <c r="CR40" s="54" t="n"/>
     </row>
     <row r="41">
       <c r="B41" s="66" t="n"/>
@@ -4916,6 +4960,15 @@
       </c>
       <c r="AQ43" s="58" t="n"/>
     </row>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
     <row r="53">
       <c r="B53" s="66" t="n"/>
     </row>
@@ -5791,6 +5844,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="V8" s="111" t="inlineStr">
+        <is>
+          <t>SDLoss</t>
+        </is>
+      </c>
+      <c r="W8" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
       <c r="AB8" s="111" t="inlineStr">
         <is>
           <t>Loss</t>
@@ -5839,6 +5902,16 @@
         </is>
       </c>
       <c r="K9" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="V9" s="111" t="inlineStr">
+        <is>
+          <t>MaxLoss</t>
+        </is>
+      </c>
+      <c r="W9" s="111" t="inlineStr">
         <is>
           <t>float</t>
         </is>
@@ -6129,7 +6202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:I159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -6174,6 +6247,7 @@
     <row r="5">
       <c r="C5" s="7" t="n"/>
     </row>
+    <row r="6"/>
     <row r="7" ht="32" customFormat="1" customHeight="1" s="66">
       <c r="B7" s="68" t="inlineStr">
         <is>
@@ -10354,66 +10428,66 @@
       </c>
     </row>
     <row r="125">
-      <c r="B125" t="inlineStr">
+      <c r="B125" s="76" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>ALT</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
+      <c r="C125" s="76" t="inlineStr">
+        <is>
+          <t>EPT</t>
+        </is>
+      </c>
+      <c r="D125" s="76" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>LossMethod</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>LossType</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>String code for loss calculation method: MEAN (analytical mean), STOC (stochastic sampling), CONV (numerical convolution).</t>
+      <c r="E125" s="76" t="inlineStr">
+        <is>
+          <t>SDLoss</t>
+        </is>
+      </c>
+      <c r="G125" s="38" t="inlineStr">
+        <is>
+          <t>Optional. Sample standard deviation of loss at this return period, around the sample mean EP curve (most relevant to EPMethod S_MEAN). Populated only where the producing platform calculates it; null otherwise.</t>
         </is>
       </c>
       <c r="H125" s="38" t="inlineStr">
         <is>
-          <t>Renamed from LossType in ORD v2; MEAN was ANLM in ORD v1</t>
+          <t>New in ORD v2</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" t="inlineStr">
+      <c r="B126" s="76" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>GPLT,GALT,GEPT</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
+      <c r="C126" s="76" t="inlineStr">
+        <is>
+          <t>EPT</t>
+        </is>
+      </c>
+      <c r="D126" s="76" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>GroupMethod</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>String code for grouped-analysis calculation method: MEAN, RSAM, RSSD. Used on grouped output tables in place of EPMethod (no EP variants needed); MEAN LossMethod is excluded as a GroupMethod.</t>
+      <c r="E126" s="76" t="inlineStr">
+        <is>
+          <t>MaxLoss</t>
+        </is>
+      </c>
+      <c r="G126" s="38" t="inlineStr">
+        <is>
+          <t>Optional. Maximum loss at this return period, around the sample mean EP curve (most relevant to EPMethod S_MEAN). Populated only where the producing platform calculates it; null otherwise.</t>
         </is>
       </c>
       <c r="H126" s="38" t="inlineStr">
@@ -10435,40 +10509,108 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
+          <t>ALT</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LossMethod</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>LossType</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>String code for loss calculation method: MEAN (analytical mean), STOC (stochastic sampling), CONV (numerical convolution).</t>
+        </is>
+      </c>
+      <c r="H127" s="38" t="inlineStr">
+        <is>
+          <t>Renamed from LossType in ORD v2; MEAN was ANLM in ORD v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
           <t>GPLT,GALT,GEPT</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D128" t="inlineStr">
         <is>
           <t>csv</t>
         </is>
       </c>
-      <c r="E127" t="inlineStr">
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>GroupMethod</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>String code for grouped-analysis calculation method: MEAN, RSAM, RSSD. Used on grouped output tables in place of EPMethod (no EP variants needed); MEAN LossMethod is excluded as a GroupMethod.</t>
+        </is>
+      </c>
+      <c r="H128" s="38" t="inlineStr">
+        <is>
+          <t>New in ORD v2</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>GPLT,GALT,GEPT</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>csv</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
         <is>
           <t>GroupEventSetId</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="G129" t="inlineStr">
         <is>
           <t>Identifier of the GroupEventSet: the set of analyses with compatible event sets that were combined in the grouped analysis. Opaque string whose structure is platform-specific; compare it as a whole and never parse it.</t>
         </is>
       </c>
-      <c r="H127" s="38" t="inlineStr">
+      <c r="H129" s="38" t="inlineStr">
         <is>
           <t>New in ORD v2</t>
         </is>
       </c>
-      <c r="I127" t="inlineStr">
+      <c r="I129" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-    </row>
-    <row r="128">
-      <c r="H128" s="38" t="n"/>
-    </row>
-    <row r="129">
-      <c r="H129" s="38" t="n"/>
     </row>
     <row r="130">
       <c r="H130" s="38" t="n"/>
@@ -10553,6 +10695,12 @@
     </row>
     <row r="157">
       <c r="H157" s="38" t="n"/>
+    </row>
+    <row r="158">
+      <c r="H158" s="38" t="n"/>
+    </row>
+    <row r="159">
+      <c r="H159" s="38" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="B7:I124"/>

--- a/Docs/ORD_Data_Spec.xlsx
+++ b/Docs/ORD_Data_Spec.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perspectives" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tables'!$B$4:$H$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tables'!$B$4:$H$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'ListOfFields'!$B$7:$I$124</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -1248,7 +1248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:H59"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -1268,6 +1268,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="16" customHeight="1" s="61">
       <c r="B3" s="13" t="n"/>
     </row>
@@ -1710,33 +1711,36 @@
       </c>
     </row>
     <row r="17" ht="32" customHeight="1" s="61">
-      <c r="B17" s="32" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>Results</t>
         </is>
       </c>
-      <c r="C17" s="33" t="inlineStr">
-        <is>
-          <t>Error Log</t>
-        </is>
-      </c>
-      <c r="D17" s="54" t="inlineStr">
-        <is>
-          <t>ELOG</t>
-        </is>
-      </c>
-      <c r="E17" s="33" t="inlineStr">
-        <is>
-          <t>Contains error codes for locations that were failed to be processed by the model</t>
-        </is>
-      </c>
-      <c r="F17" s="34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G17" s="34" t="n"/>
-      <c r="H17" s="33" t="n"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Group Event Loss Table</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>GELT</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Grouped event losses combining compatible analyses (ORD v2); uses GroupMethod (MEAN or RSSD only, not valid for RSAM) and requires GroupEventSetId</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>GroupMethod column (new in ORD v2)</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="32" customHeight="1" s="61">
       <c r="B18" s="32" t="inlineStr">
@@ -1746,22 +1750,22 @@
       </c>
       <c r="C18" s="33" t="inlineStr">
         <is>
-          <t>Aggregate summaries of exposure within model domain</t>
+          <t>Error Log</t>
         </is>
       </c>
       <c r="D18" s="54" t="inlineStr">
         <is>
-          <t>DOMEXP</t>
+          <t>ELOG</t>
         </is>
       </c>
       <c r="E18" s="33" t="inlineStr">
         <is>
-          <t>Model specific so needs to be in the Results area</t>
+          <t>Contains error codes for locations that were failed to be processed by the model</t>
         </is>
       </c>
       <c r="F18" s="34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="34" t="n"/>
@@ -1775,12 +1779,12 @@
       </c>
       <c r="C19" s="33" t="inlineStr">
         <is>
-          <t>Aggregate summaries of rejected exposure by reason rejected</t>
+          <t>Aggregate summaries of exposure within model domain</t>
         </is>
       </c>
       <c r="D19" s="54" t="inlineStr">
         <is>
-          <t>REJEXP</t>
+          <t>DOMEXP</t>
         </is>
       </c>
       <c r="E19" s="33" t="inlineStr">
@@ -1797,49 +1801,49 @@
       <c r="H19" s="33" t="n"/>
     </row>
     <row r="20" ht="16" customHeight="1" s="61">
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>Analysis</t>
-        </is>
-      </c>
-      <c r="C20" s="75" t="inlineStr">
-        <is>
-          <t>Analysis MetaData json blob - see example</t>
-        </is>
-      </c>
-      <c r="D20" s="37" t="n"/>
-      <c r="E20" s="38" t="inlineStr">
-        <is>
-          <t>File that includes metadata for each analysis. It ties everything together and enables full audit trail.</t>
-        </is>
-      </c>
-      <c r="F20" s="41" t="inlineStr">
-        <is>
-          <t>partly</t>
-        </is>
-      </c>
-      <c r="G20" s="41" t="inlineStr">
-        <is>
-          <t>analysis_settings</t>
-        </is>
-      </c>
-      <c r="H20" s="38" t="n"/>
+      <c r="B20" s="32" t="inlineStr">
+        <is>
+          <t>Results</t>
+        </is>
+      </c>
+      <c r="C20" s="33" t="inlineStr">
+        <is>
+          <t>Aggregate summaries of rejected exposure by reason rejected</t>
+        </is>
+      </c>
+      <c r="D20" s="54" t="inlineStr">
+        <is>
+          <t>REJEXP</t>
+        </is>
+      </c>
+      <c r="E20" s="33" t="inlineStr">
+        <is>
+          <t>Model specific so needs to be in the Results area</t>
+        </is>
+      </c>
+      <c r="F20" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="33" t="n"/>
     </row>
     <row r="21" ht="16" customHeight="1" s="61">
       <c r="B21" s="35" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>Analysis</t>
         </is>
       </c>
       <c r="C21" s="75" t="inlineStr">
         <is>
-          <t>Model MetaData json blob - not done yet</t>
+          <t>Analysis MetaData json blob - see example</t>
         </is>
       </c>
       <c r="D21" s="37" t="n"/>
       <c r="E21" s="38" t="inlineStr">
         <is>
-          <t>A file that gives mandatory information about each model, including name, version number, frequency, severity and seasonality usage</t>
+          <t>File that includes metadata for each analysis. It ties everything together and enables full audit trail.</t>
         </is>
       </c>
       <c r="F21" s="41" t="inlineStr">
@@ -1847,7 +1851,11 @@
           <t>partly</t>
         </is>
       </c>
-      <c r="G21" s="41" t="n"/>
+      <c r="G21" s="41" t="inlineStr">
+        <is>
+          <t>analysis_settings</t>
+        </is>
+      </c>
       <c r="H21" s="38" t="n"/>
     </row>
     <row r="22" ht="16" customHeight="1" s="61">
@@ -1856,20 +1864,20 @@
           <t>Model</t>
         </is>
       </c>
-      <c r="C22" s="38" t="inlineStr">
-        <is>
-          <t>Event</t>
+      <c r="C22" s="75" t="inlineStr">
+        <is>
+          <t>Model MetaData json blob - not done yet</t>
         </is>
       </c>
       <c r="D22" s="37" t="n"/>
       <c r="E22" s="38" t="inlineStr">
         <is>
-          <t>Contains the full set of events with optional event descriptions and the event rate provided by the modeller as well as, optionally, an OriginalEventRate field</t>
+          <t>A file that gives mandatory information about each model, including name, version number, frequency, severity and seasonality usage</t>
         </is>
       </c>
       <c r="F22" s="41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>partly</t>
         </is>
       </c>
       <c r="G22" s="41" t="n"/>
@@ -1883,13 +1891,13 @@
       </c>
       <c r="C23" s="38" t="inlineStr">
         <is>
-          <t>Occurrence</t>
+          <t>Event</t>
         </is>
       </c>
       <c r="D23" s="37" t="n"/>
       <c r="E23" s="38" t="inlineStr">
         <is>
-          <t>If we add an optional quantile column and then this can also serve as the RMS style PEQT</t>
+          <t>Contains the full set of events with optional event descriptions and the event rate provided by the modeller as well as, optionally, an OriginalEventRate field</t>
         </is>
       </c>
       <c r="F23" s="41" t="inlineStr">
@@ -1908,13 +1916,13 @@
       </c>
       <c r="C24" s="38" t="inlineStr">
         <is>
-          <t>Event Footprint</t>
+          <t>Occurrence</t>
         </is>
       </c>
       <c r="D24" s="37" t="n"/>
       <c r="E24" s="38" t="inlineStr">
         <is>
-          <t>Contains information about the footprint of each event</t>
+          <t>If we add an optional quantile column and then this can also serve as the RMS style PEQT</t>
         </is>
       </c>
       <c r="F24" s="41" t="inlineStr">
@@ -1933,13 +1941,13 @@
       </c>
       <c r="C25" s="38" t="inlineStr">
         <is>
-          <t>Vulnerability</t>
+          <t>Event Footprint</t>
         </is>
       </c>
       <c r="D25" s="37" t="n"/>
       <c r="E25" s="38" t="inlineStr">
         <is>
-          <t>Contains information about each vulnerability curve</t>
+          <t>Contains information about the footprint of each event</t>
         </is>
       </c>
       <c r="F25" s="41" t="inlineStr">
@@ -1958,13 +1966,13 @@
       </c>
       <c r="C26" s="38" t="inlineStr">
         <is>
-          <t>Period Weights</t>
+          <t>Vulnerability</t>
         </is>
       </c>
       <c r="D26" s="37" t="n"/>
       <c r="E26" s="38" t="inlineStr">
         <is>
-          <t>Or we could include PeriodWeight as an optional column in the Occurrence file</t>
+          <t>Contains information about each vulnerability curve</t>
         </is>
       </c>
       <c r="F26" s="41" t="inlineStr">
@@ -1976,29 +1984,29 @@
       <c r="H26" s="38" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="32" t="inlineStr">
-        <is>
-          <t>Exposure</t>
-        </is>
-      </c>
-      <c r="C27" s="33" t="inlineStr">
-        <is>
-          <t>Input Exposure</t>
-        </is>
-      </c>
-      <c r="D27" s="54" t="n"/>
-      <c r="E27" s="33" t="inlineStr">
-        <is>
-          <t>Table for each input file: 2 or 4 for OED (with &amp; without RI),  different numbers of files for other vendors</t>
-        </is>
-      </c>
-      <c r="F27" s="34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="G27" s="34" t="n"/>
-      <c r="H27" s="33" t="n"/>
+      <c r="B27" s="35" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C27" s="38" t="inlineStr">
+        <is>
+          <t>Period Weights</t>
+        </is>
+      </c>
+      <c r="D27" s="37" t="n"/>
+      <c r="E27" s="38" t="inlineStr">
+        <is>
+          <t>Or we could include PeriodWeight as an optional column in the Occurrence file</t>
+        </is>
+      </c>
+      <c r="F27" s="41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G27" s="41" t="n"/>
+      <c r="H27" s="38" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="32" t="inlineStr">
@@ -2008,13 +2016,13 @@
       </c>
       <c r="C28" s="33" t="inlineStr">
         <is>
-          <t>Aggregated Exposure</t>
+          <t>Input Exposure</t>
         </is>
       </c>
       <c r="D28" s="54" t="n"/>
       <c r="E28" s="33" t="inlineStr">
         <is>
-          <t>Aggregate summaries of input exposure</t>
+          <t>Table for each input file: 2 or 4 for OED (with &amp; without RI),  different numbers of files for other vendors</t>
         </is>
       </c>
       <c r="F28" s="34" t="inlineStr">
@@ -2026,32 +2034,51 @@
       <c r="H28" s="33" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="32" t="inlineStr">
+        <is>
+          <t>Exposure</t>
+        </is>
+      </c>
+      <c r="C29" s="33" t="inlineStr">
+        <is>
+          <t>Aggregated Exposure</t>
+        </is>
+      </c>
+      <c r="D29" s="54" t="n"/>
+      <c r="E29" s="33" t="inlineStr">
+        <is>
+          <t>Aggregate summaries of input exposure</t>
+        </is>
+      </c>
+      <c r="F29" s="34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G29" s="34" t="n"/>
+      <c r="H29" s="33" t="n"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="35" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C29" s="38" t="inlineStr">
+      <c r="C30" s="38" t="inlineStr">
         <is>
           <t>Shapefiles</t>
         </is>
       </c>
-      <c r="E29" s="38" t="inlineStr">
+      <c r="E30" s="38" t="inlineStr">
         <is>
           <t>The possibility of including shapefiles should be included</t>
         </is>
       </c>
-      <c r="F29" s="41" t="inlineStr">
+      <c r="F30" s="41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="G29" s="41" t="n"/>
-      <c r="H29" s="38" t="n"/>
-    </row>
-    <row r="30">
-      <c r="E30" s="38" t="n"/>
-      <c r="F30" s="38" t="n"/>
       <c r="G30" s="41" t="n"/>
       <c r="H30" s="38" t="n"/>
     </row>
@@ -2229,8 +2256,14 @@
       <c r="G59" s="41" t="n"/>
       <c r="H59" s="38" t="n"/>
     </row>
+    <row r="60">
+      <c r="E60" s="38" t="n"/>
+      <c r="F60" s="38" t="n"/>
+      <c r="G60" s="41" t="n"/>
+      <c r="H60" s="38" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="B4:H26"/>
+  <autoFilter ref="B4:H27"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511805555555555" footer="0.511805555555555"/>
   <pageSetup orientation="portrait" paperSize="9" firstPageNumber="0" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -2342,19 +2375,15 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="B5" s="86" t="n"/>
     </row>
     <row r="6">
       <c r="B6" s="86" t="n"/>
     </row>
-    <row r="7"/>
-    <row r="8"/>
     <row r="9">
       <c r="CI9" s="86" t="n"/>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="B11" s="66" t="inlineStr">
         <is>
@@ -4960,15 +4989,6 @@
       </c>
       <c r="AQ43" s="58" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
     <row r="53">
       <c r="B53" s="66" t="n"/>
     </row>
@@ -4984,7 +5004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI19"/>
+  <dimension ref="A1:AL19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="13"/>
   <cols>
     <col width="21.1640625" customWidth="1" style="111" min="1" max="1"/>
@@ -5017,6 +5037,8 @@
     <col width="13" customWidth="1" style="61" min="34" max="34"/>
     <col width="13" customWidth="1" style="61" min="35" max="35"/>
     <col width="13" customWidth="1" style="61" min="36" max="36"/>
+    <col width="13" customWidth="1" style="61" min="37" max="37"/>
+    <col width="13" customWidth="1" style="61" min="38" max="38"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5080,6 +5102,11 @@
           <t>GEPT</t>
         </is>
       </c>
+      <c r="AK1" s="113" t="inlineStr">
+        <is>
+          <t>GELT</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="112" t="inlineStr">
@@ -5202,6 +5229,16 @@
           <t>Data Type</t>
         </is>
       </c>
+      <c r="AK2" s="112" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="AL2" s="112" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="111" t="inlineStr">
@@ -5324,6 +5361,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AK3" s="111" t="inlineStr">
+        <is>
+          <t>GroupEventSetId</t>
+        </is>
+      </c>
+      <c r="AL3" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="111" t="inlineStr">
@@ -5446,6 +5493,16 @@
           <t>32-bit integer</t>
         </is>
       </c>
+      <c r="AK4" s="111" t="inlineStr">
+        <is>
+          <t>SummaryId</t>
+        </is>
+      </c>
+      <c r="AL4" s="111" t="inlineStr">
+        <is>
+          <t>32-bit integer</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="111" t="inlineStr">
@@ -5568,6 +5625,16 @@
           <t>string</t>
         </is>
       </c>
+      <c r="AK5" s="111" t="inlineStr">
+        <is>
+          <t>EventId</t>
+        </is>
+      </c>
+      <c r="AL5" s="111" t="inlineStr">
+        <is>
+          <t>32-bit integer</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="111" t="inlineStr">
@@ -5690,6 +5757,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK6" s="111" t="inlineStr">
+        <is>
+          <t>GroupMethod</t>
+        </is>
+      </c>
+      <c r="AL6" s="111" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="111" t="inlineStr">
@@ -5802,6 +5879,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK7" s="111" t="inlineStr">
+        <is>
+          <t>EventRate</t>
+        </is>
+      </c>
+      <c r="AL7" s="111" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="111" t="inlineStr">
@@ -5864,6 +5951,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>ChanceOfLoss</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="111" t="inlineStr">
@@ -5916,6 +6013,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>MeanLoss</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="111" t="inlineStr">
@@ -5958,6 +6065,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>SDLoss</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="111" t="inlineStr">
@@ -6000,6 +6117,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>MaxLoss</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="111" t="inlineStr">
@@ -6042,6 +6169,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>FootprintExposure</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="111" t="inlineStr">
@@ -6084,6 +6221,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>MeanImpactedExposure</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="111" t="inlineStr">
@@ -6106,6 +6253,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>MaxImpactedExposure</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="111" t="inlineStr">
@@ -6118,6 +6275,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>SDLossCor</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="111" t="inlineStr">
@@ -6130,6 +6297,16 @@
           <t>float</t>
         </is>
       </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>SDLossInd</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="111" t="inlineStr">
@@ -6168,13 +6345,14 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="13">
     <mergeCell ref="AB1:AC1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="V1:W1"/>
     <mergeCell ref="S1:T1"/>
     <mergeCell ref="AH1:AI1"/>
+    <mergeCell ref="AK1:AL1"/>
     <mergeCell ref="J1:K1"/>
     <mergeCell ref="Y1:Z1"/>
     <mergeCell ref="P1:Q1"/>
@@ -6202,7 +6380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I159"/>
+  <dimension ref="B1:I159"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="2.6640625" customWidth="1" style="61" min="1" max="1"/>
@@ -6298,7 +6476,7 @@
       </c>
       <c r="C8" s="76" t="inlineStr">
         <is>
-          <t>ALT,EPT,PSEPT,MELT,MPLT,SELT,SPLT,QELT,QPLT,GPLT,GALT,GEPT</t>
+          <t>ALT,EPT,PSEPT,MELT,MPLT,SELT,SPLT,QELT,QPLT,GPLT,GALT,GEPT,GELT</t>
         </is>
       </c>
       <c r="D8" s="76" t="inlineStr">
@@ -6368,7 +6546,7 @@
       </c>
       <c r="C10" s="76" t="inlineStr">
         <is>
-          <t>ALT,MELT,MPLT,GALT</t>
+          <t>ALT,MELT,MPLT,GALT,GELT</t>
         </is>
       </c>
       <c r="D10" s="76" t="inlineStr">
@@ -6401,7 +6579,7 @@
       </c>
       <c r="C11" s="76" t="inlineStr">
         <is>
-          <t>ALT,MELT,MPLT,GALT</t>
+          <t>ALT,MELT,MPLT,GALT,GELT</t>
         </is>
       </c>
       <c r="D11" s="76" t="inlineStr">
@@ -6467,7 +6645,7 @@
       </c>
       <c r="C13" s="76" t="inlineStr">
         <is>
-          <t>MELT,MPLT</t>
+          <t>MELT,MPLT,GELT</t>
         </is>
       </c>
       <c r="D13" s="76" t="inlineStr">
@@ -6673,7 +6851,7 @@
       </c>
       <c r="C19" s="76" t="inlineStr">
         <is>
-          <t>MELT,MPLT,SELT,SPLT,QELT,QPLT,GPLT</t>
+          <t>MELT,MPLT,SELT,SPLT,QELT,QPLT,GPLT,GELT</t>
         </is>
       </c>
       <c r="D19" s="76" t="inlineStr">
@@ -6906,7 +7084,7 @@
       </c>
       <c r="C26" s="71" t="inlineStr">
         <is>
-          <t>MELT</t>
+          <t>MELT,GELT</t>
         </is>
       </c>
       <c r="D26" s="76" t="inlineStr">
@@ -7054,7 +7232,7 @@
       </c>
       <c r="C30" s="71" t="inlineStr">
         <is>
-          <t>MELT,MPLT</t>
+          <t>MELT,MPLT,GELT</t>
         </is>
       </c>
       <c r="D30" s="76" t="inlineStr">
@@ -7088,7 +7266,7 @@
       </c>
       <c r="C31" s="71" t="inlineStr">
         <is>
-          <t>MELT,MPLT</t>
+          <t>MELT,MPLT,GELT</t>
         </is>
       </c>
       <c r="D31" s="76" t="inlineStr">
@@ -10193,7 +10371,7 @@
       </c>
       <c r="C118" s="76" t="inlineStr">
         <is>
-          <t>MELT, MPLT</t>
+          <t>MELT, MPLT, GELT</t>
         </is>
       </c>
       <c r="D118" s="76" t="inlineStr">
@@ -10230,7 +10408,7 @@
       </c>
       <c r="C119" s="76" t="inlineStr">
         <is>
-          <t>MELT, MPLT</t>
+          <t>MELT, MPLT, GELT</t>
         </is>
       </c>
       <c r="D119" s="76" t="inlineStr">
@@ -10267,7 +10445,7 @@
       </c>
       <c r="C120" s="71" t="inlineStr">
         <is>
-          <t>MELT,MPLT</t>
+          <t>MELT,MPLT,GELT</t>
         </is>
       </c>
       <c r="D120" s="76" t="inlineStr">
@@ -10300,7 +10478,7 @@
       </c>
       <c r="C121" s="71" t="inlineStr">
         <is>
-          <t>MELT,MPLT</t>
+          <t>MELT,MPLT,GELT</t>
         </is>
       </c>
       <c r="D121" s="76" t="inlineStr">
@@ -10546,7 +10724,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>GPLT,GALT,GEPT</t>
+          <t>GPLT,GALT,GEPT,GELT</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10561,7 +10739,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>String code for grouped-analysis calculation method: MEAN, RSAM, RSSD. Used on grouped output tables in place of EPMethod (no EP variants needed); MEAN LossMethod is excluded as a GroupMethod.</t>
+          <t>String code for grouped-analysis calculation method: MEAN, RSAM, RSSD. Used on grouped output tables in place of EPMethod (no EP variants needed); MEAN LossMethod is excluded as a GroupMethod. GELT is valid for MEAN and RSSD only, not RSAM.</t>
         </is>
       </c>
       <c r="H128" s="38" t="inlineStr">
@@ -10583,7 +10761,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>GPLT,GALT,GEPT</t>
+          <t>GPLT,GALT,GEPT,GELT</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
